--- a/WorkBot/main/data/order_archive/Hill & Markes/Hill & Markes_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Hill & Markes/Hill & Markes_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,258 +752,6 @@
         <v>24.27</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>INPSMR0080SH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cup - Hot (8oz)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>54.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SAB94160B50</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Square Serving Bowl - 160oz</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="E20" t="n">
-        <v>45.18</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TS12</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tamper Evident - 12oz Square</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="E21" t="n">
-        <v>115.17</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TS16</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Tamper Evident - 16oz</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>41.88</v>
-      </c>
-      <c r="E22" t="n">
-        <v>125.64</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TS8</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Tamper Evident - 8oz</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>114.9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>HIMF1824XC</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bag - Poly (10x8x24, 1.25mil)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>77.86</v>
-      </c>
-      <c r="E24" t="n">
-        <v>77.86</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6G063015</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bag Poly - 6x3x15 LW</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="E25" t="n">
-        <v>54.56</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>P4040XC</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bag Sheet Pan Cover 30x43</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>22.04</v>
-      </c>
-      <c r="E26" t="n">
-        <v>66.12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PRI80134X60</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Masking Tape</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="E27" t="n">
-        <v>63.64</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>K250</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Towel Paper Roll (White)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>33.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>33.15</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WES123</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Wrap - Film (12")</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="E29" t="n">
-        <v>19.53</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>WES183</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Wrap - Film (18")</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>42.28</v>
-      </c>
-      <c r="E30" t="n">
-        <v>42.28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
